--- a/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LUMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>LUMN</t>
   </si>
@@ -656,421 +656,433 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2805000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2899000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3041000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3087000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3092000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3182000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3329000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3221000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3268000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3290000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3517000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3641000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3661000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3738000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3800000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4390000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4612000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4676000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4847000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4887000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4924000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5029000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5125000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5167000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5192000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5228000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5306000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5350000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5375000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5427000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5778000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1415000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1435000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1627000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1700000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1624000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1687000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1706000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1692000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1653000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1652000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1737000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1850000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1740000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1817000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1826000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1999000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2058000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1985000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2086000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2151000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2115000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2136000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2231000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2236000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2232000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2235000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2257000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2334000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2243000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2300000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2657000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1390000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1464000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1414000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1387000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1468000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1495000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1623000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1529000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1615000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1638000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1780000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1791000</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1921000</v>
       </c>
       <c r="P10" s="3">
         <v>1921000</v>
       </c>
       <c r="Q10" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="R10" s="3">
         <v>1974000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2391000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2554000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2691000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2761000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2736000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2809000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2893000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2894000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2931000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2960000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2993000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3049000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3016000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3132000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3127000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3121000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1104,8 +1116,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1199,8 +1212,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1294,62 +1310,65 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-370000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>138000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>395000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>864000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>35000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>59000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-190000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-273000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2006000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>37000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8795000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-452000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3504000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-639000</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1360,23 +1379,23 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2665000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>7000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>79000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
@@ -1384,108 +1403,114 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>6506000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2692000</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>668000</v>
+      </c>
+      <c r="E15" s="3">
         <v>664000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>674000</v>
       </c>
       <c r="F15" s="3">
         <v>674000</v>
       </c>
       <c r="G15" s="3">
+        <v>674000</v>
+      </c>
+      <c r="H15" s="3">
         <v>688000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>713000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>758000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>707000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>743000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>748000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>751000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>755000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>746000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>733000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>796000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>808000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>827000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>808000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>877000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>951000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1041000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1150000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1195000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1193000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1162000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1160000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1210000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1235000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1196000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1188000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>2003000</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1516,198 +1541,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2886000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2919000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3223000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3249000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3113000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3121000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3083000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3133000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3175000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3262000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3585000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3357000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3315000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3310000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6797000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2960000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3700000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3593000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3686000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3756000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3918000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4034000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6957000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4275000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4296000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4327000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4459000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4400000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4399000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10926000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7585000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-20000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-182000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-162000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-21000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>61000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>246000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>88000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>93000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>28000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-68000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>284000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>346000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>428000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2997000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1430000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>912000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1083000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1161000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1131000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1006000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>995000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1832000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>892000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>896000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>901000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>847000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>950000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>976000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-5499000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1807000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1741,483 +1773,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-38000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-75000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-45000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-54000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-55000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-22000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-81000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-35000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-34000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-202000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>41000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-49000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-66000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>95000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-130000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-122000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>70000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-110000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-38000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>52000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>26000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>20000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>31000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-44000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>44000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>605000</v>
+      </c>
+      <c r="E21" s="3">
         <v>682000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>567000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>557000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>721000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>829000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1026000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>876000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>871000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>810000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>885000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>998000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1141000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1227000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2106000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2108000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1617000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1961000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1928000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2044000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2099000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2171000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-617000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2082000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2089000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2042000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2046000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2141000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2216000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-4316000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-564000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E22" s="3">
         <v>225000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>280000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>319000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>338000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>347000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>357000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>351000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>373000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>291000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>290000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>295000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>294000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>279000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>280000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>363000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>337000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>352000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>372000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>377000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>384000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>389000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>396000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>409000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>414000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>449000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>487000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>496000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>518000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>523000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>539000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-255000</v>
+      </c>
+      <c r="E23" s="3">
         <v>177000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-509000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-813000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1149000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-245000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-119000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-172000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-41000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>102000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2142000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-85000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8690000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>680000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3182000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>937000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>453000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>801000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>679000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>716000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>674000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>632000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2208000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>480000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>513000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>433000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>349000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>410000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>502000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-6027000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2365000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="E24" s="3">
         <v>377000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-507000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-192000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-234000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-44000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-204000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-24000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>45000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-147000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-7000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>46000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>169000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-113000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>359000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>109000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>202000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>171000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>172000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>168000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>157000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>81000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>114000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>136000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>119000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>126000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>108000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>131000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>138000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2311,198 +2359,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-200000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-621000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-915000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-201000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>85000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-148000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-49000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>57000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1995000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-78000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8736000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>511000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3069000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>578000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>344000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>599000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>508000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>544000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>506000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>475000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>366000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>377000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>314000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>223000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>302000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>371000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-200000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-621000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-915000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-201000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>85000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-148000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-49000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>57000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1995000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-78000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8736000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>511000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3069000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>578000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>344000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>599000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>508000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>544000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>506000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>475000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>366000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>377000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>314000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>223000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>302000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>371000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2403000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2596,8 +2653,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2670,8 +2730,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2688,11 +2748,14 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2786,8 +2849,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2881,198 +2947,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E32" s="3">
         <v>38000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>75000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>45000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>54000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>55000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>22000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>81000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>35000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>34000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>202000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-41000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>49000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>66000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-95000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>130000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>122000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-70000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>110000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>38000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-52000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-26000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>19000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>11000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>44000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-44000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>5000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-200000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-621000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-915000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-201000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>85000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-148000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-49000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>57000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1995000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-78000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8736000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>511000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3069000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>578000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>344000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>599000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>508000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>544000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>506000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>475000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>366000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>377000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>314000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>223000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>302000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>371000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3166,203 +3241,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-200000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-621000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-915000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-201000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>85000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-148000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-49000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>57000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1995000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-78000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8736000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>511000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3069000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>578000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>344000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>599000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>508000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>544000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>506000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>475000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>366000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>377000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>314000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>223000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>302000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>371000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3396,8 +3480,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3431,103 +3516,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1876000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1625000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1003000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2401000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1568000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1900000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1889000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2640000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1495000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1580000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2234000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>311000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>411000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1148000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1251000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>252000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>360000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>366000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>354000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>635000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>935000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>486000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>406000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>526000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1763000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1564000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1404000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>410000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>441000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3621,388 +3710,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1406000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1629000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1800000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1721000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1692000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1580000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1730000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1254000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1351000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1369000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1610000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1553000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1581000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1450000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1528000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1552000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1529000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1586000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1723000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1605000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1970000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1953000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2035000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2184000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2284000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2281000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2336000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2346000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2590000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2474000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2614000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E44" s="3">
         <v>132000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>165000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>163000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>126000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>124000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>146000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>173000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>184000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>193000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>209000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>227000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>205000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>223000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>236000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>179000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>151000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>128000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>96000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>103000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>114000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>100000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>105000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>112000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>122000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>119000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>105000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>137000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>151000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>154000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>120000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E45" s="3">
         <v>262000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4537000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4052000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3931000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>262000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>257000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>312000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>313000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>312000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>327000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2163000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2220000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2174000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2436000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7399000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9750000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9692000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9363000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9358000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>727000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>754000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>630000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>682000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>689000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>726000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>637000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>702000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>727000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>751000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>598000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4109000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4121000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7909000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8707000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7737000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4277000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4394000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4736000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3760000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3935000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4775000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4646000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4873000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5405000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5451000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9382000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>11790000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>11772000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11536000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11701000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3746000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3293000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3176000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3504000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4858000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4690000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4768000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4589000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3878000</v>
-      </c>
-      <c r="AF46" s="3">
-        <v>3820000</v>
       </c>
       <c r="AG46" s="3">
         <v>3820000</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>3820000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4045,8 +4149,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4096,198 +4200,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20300000</v>
+      </c>
+      <c r="E48" s="3">
         <v>19926000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20866000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19107000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>18665000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20568000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21540000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20344000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20089000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19908000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20988000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19606000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19432000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19321000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20506000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20713000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20720000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20829000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>22346000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20926000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>25993000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>26091000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>28037000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>26290000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>26079000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>27623000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>27765000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>27595000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>27704000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>27745000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>26408000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4040000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4240000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4463000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4411000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4525000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6624000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6770000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6931000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7091000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7254000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7434000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9608000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9763000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18691000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>18823000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>22354000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>22575000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>22761000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>22956000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23147000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>26530000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>26738000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>27089000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>30039000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>30372000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>30699000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>31101000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>31386000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>31734000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>32035000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>38810000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4381,8 +4494,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4476,103 +4592,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2333000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2335000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>959000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2061000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2049000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2069000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>696000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1978000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2003000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2076000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>821000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1898000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1941000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1957000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>832000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2368000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2590000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2675000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1155000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2534000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2678000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2706000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1092000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2766000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2862000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1044000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1108000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1158000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1192000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1188000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1218000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4666,103 +4788,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30782000</v>
+      </c>
+      <c r="E54" s="3">
         <v>30622000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>34342000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>34286000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32976000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33538000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33496000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33989000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32943000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33173000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>34018000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35921000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36168000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>45530000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>45612000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>54817000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>57675000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>58037000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>57993000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>58308000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>58947000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>58828000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>59394000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>62599000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>64171000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>64056000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>64742000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>64728000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>64508000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>64788000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>70256000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4796,8 +4924,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4831,578 +4960,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1035000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1227000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1508000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1089000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>831000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>773000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>749000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>905000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>995000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1162000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1134000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1015000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1171000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1131000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1044000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1009000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1053000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>902000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>758000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>829000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>966000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1017000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1134000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1364000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1448000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1581000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1724000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1712000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1634000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1481000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1933000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E58" s="3">
         <v>325000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>354000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>367000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>606000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>593000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>665000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>678000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>473000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>368000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>425000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>451000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>477000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>479000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>154000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3474000</v>
-      </c>
-      <c r="S58" s="3">
-        <v>156000</v>
       </c>
       <c r="T58" s="3">
         <v>156000</v>
       </c>
       <c r="U58" s="3">
+        <v>156000</v>
+      </c>
+      <c r="V58" s="3">
         <v>1554000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2501000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2595000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3841000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2427000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1487000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2885000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1129000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2300000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1744000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1595000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>632000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>652000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2053000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1871000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1525000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1583000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1456000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1379000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1312000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1421000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1446000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1598000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1111000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1582000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1534000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2560000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3699000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4232000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4572000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4597000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4857000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4970000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2949000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2929000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3073000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3028000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3139000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2993000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3234000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3133000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3266000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3260000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2946000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4263000</v>
+      </c>
+      <c r="E60" s="3">
         <v>4171000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4390000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3932000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3632000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3545000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3639000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3940000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3738000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3816000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3534000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3920000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3963000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4848000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4897000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8715000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5781000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5655000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7169000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8300000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6510000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7787000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6634000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5879000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7472000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5703000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7258000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6589000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6495000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5373000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5531000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13150000</v>
+      </c>
+      <c r="E61" s="3">
         <v>12925000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18466000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17578000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17565000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17334000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18453000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18142000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18411000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18591000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>20871000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19740000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19899000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>19743000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20418000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21764000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>27965000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>28397000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>27428000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>27260000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>28574000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>27599000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>29410000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>31105000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>31414000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>33481000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>32394000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>33381000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>33193000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>34858000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>35409000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2960000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2982000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1824000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3295000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3276000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3236000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2112000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>2637000</v>
       </c>
       <c r="K62" s="3">
         <v>2637000</v>
       </c>
       <c r="L62" s="3">
+        <v>2637000</v>
+      </c>
+      <c r="M62" s="3">
         <v>2641000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1610000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2626000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2633000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2578000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9923000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>11761000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>11710000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>11703000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11556000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11565000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>12157000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12139000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12188000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11926000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11823000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11581000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11620000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11084000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>11128000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>11014000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9488000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5496,8 +5644,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5591,8 +5742,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5686,103 +5840,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32270000</v>
+      </c>
+      <c r="E66" s="3">
         <v>31939000</v>
-      </c>
-      <c r="E66" s="3">
-        <v>35459000</v>
       </c>
       <c r="F66" s="3">
         <v>35459000</v>
       </c>
       <c r="G66" s="3">
+        <v>35459000</v>
+      </c>
+      <c r="H66" s="3">
         <v>33571000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33249000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33032000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33647000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32477000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32669000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33601000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33702000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33884000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>34535000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>35238000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>42240000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>45456000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>45755000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>46153000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>47125000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>47241000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>47525000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>48232000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>48910000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>50709000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>50765000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>51272000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>51054000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>50816000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>51245000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>50428000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5816,8 +5976,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5911,8 +6072,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6006,8 +6170,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6101,8 +6268,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6196,103 +6366,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-20102000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-19901000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-19701000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-19699000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-19078000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-18163000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-17962000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-18047000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-17899000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-17850000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-17907000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-15849000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-15771000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7035000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7609000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-4477000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5055000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5399000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5998000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6506000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7050000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-7556000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-8031000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-5743000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6109000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-6486000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-6814000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-7018000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-7321000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-7693000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-1643000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6386,8 +6562,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6481,8 +6660,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6576,103 +6758,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1488000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1317000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1117000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1173000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-595000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>289000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>464000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>342000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>466000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>504000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>417000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2219000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2284000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10995000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10374000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12577000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12219000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12282000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11840000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11183000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>11706000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11303000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11162000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13689000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13462000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13291000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13470000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13674000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13692000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13543000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>19828000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6766,203 +6954,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-200000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-621000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-915000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-201000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>85000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-148000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-49000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>57000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1995000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-78000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8736000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>511000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3069000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>578000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>344000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>599000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>508000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>544000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>506000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>475000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2289000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>366000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>377000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>314000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>223000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>302000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>371000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-6165000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2412000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6996,103 +7193,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>440000</v>
+      </c>
+      <c r="E83" s="3">
         <v>461000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>494000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>454000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>466000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>476000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>492000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>484000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>483000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>473000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>520000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>529000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>550000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>534000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>796000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>808000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>827000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>808000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>877000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>951000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1041000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1150000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1195000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1193000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1162000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1160000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1210000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1235000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1196000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1188000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1262000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7186,8 +7387,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7281,8 +7485,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7376,8 +7583,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7471,8 +7681,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7566,103 +7779,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>971000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1323000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>562000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2511000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>570000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1095000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>688000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2032000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>511000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1102000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>784000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>881000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-100000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>595000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>841000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1123000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1396000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1375000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1607000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1730000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1639000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1525000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1682000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1794000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1749000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1299000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1909000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1888000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1701000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1182000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1996000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7696,103 +7915,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-902000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-943000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1644000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1041000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-891000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-791000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-915000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-850000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-753000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-713000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-821000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-843000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-796000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-640000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-833000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-845000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-761000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-577000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-848000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-690000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-646000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-716000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-758000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-988000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1009000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-974000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-940000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-957000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-800000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-931000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-915000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7886,8 +8109,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7981,103 +8207,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-894000</v>
+      </c>
+      <c r="E94" s="3">
         <v>4050000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1636000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1027000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-873000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-769000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-831000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-805000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-496000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-698000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1031000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-827000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-789000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-616000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>4882000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1864000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-701000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-569000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-763000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-654000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-620000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-675000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-724000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-942000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-959000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-939000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-899000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-954000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-811000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-906000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-882000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8111,19 +8343,20 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>1000</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>8</v>
@@ -8131,20 +8364,20 @@
       <c r="H96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>3000</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>3000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>1000</v>
       </c>
       <c r="N96" s="3">
         <v>1000</v>
@@ -8153,61 +8386,64 @@
         <v>1000</v>
       </c>
       <c r="P96" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>8000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-255000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-254000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-271000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-253000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-266000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-274000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-294000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-272000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-275000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-291000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-271000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-275000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-269000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-285000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-577000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8301,8 +8537,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8396,8 +8635,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8491,103 +8733,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4751000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-324000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-651000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-30000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-314000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-610000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-81000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1060000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>83000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-173000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>158000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-86000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4681000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3143000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-713000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-776000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1139000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1318000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-576000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-774000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1078000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2089000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-597000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-486000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-724000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>57000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-924000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-320000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8630,8 +8878,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8681,99 +8929,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E102" s="3">
         <v>622000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1398000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>833000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-333000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-753000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1146000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-85000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-656000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1898000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-119000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-731000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-107000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1042000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-156000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-18000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>30000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-295000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-242000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>443000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>76000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-120000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1237000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>193000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-126000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>286000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>991000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-44000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>98000</v>
       </c>
     </row>
